--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/74.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/74.xlsx
@@ -426,13 +426,13 @@
         <v>-5.716343082772169</v>
       </c>
       <c r="E2">
-        <v>-18.17198031501141</v>
+        <v>-21.65811281796624</v>
       </c>
       <c r="F2">
-        <v>-5.066906183474466</v>
+        <v>-5.628889770538859</v>
       </c>
       <c r="G2">
-        <v>-9.011080991467834</v>
+        <v>-12.52327848062711</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.282948390677141</v>
       </c>
       <c r="E3">
-        <v>-19.21328027070517</v>
+        <v>-24.50722035378808</v>
       </c>
       <c r="F3">
-        <v>-5.107209123463528</v>
+        <v>-5.490492086147478</v>
       </c>
       <c r="G3">
-        <v>-8.838753853966612</v>
+        <v>-11.51175453328495</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.963055971338241</v>
       </c>
       <c r="E4">
-        <v>-18.96070010445335</v>
+        <v>-22.9294230254576</v>
       </c>
       <c r="F4">
-        <v>-4.914296322197933</v>
+        <v>-6.239035042271201</v>
       </c>
       <c r="G4">
-        <v>-8.871961936271042</v>
+        <v>-10.96062153299817</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.792461697350456</v>
       </c>
       <c r="E5">
-        <v>-20.16657839100787</v>
+        <v>-22.36473590212313</v>
       </c>
       <c r="F5">
-        <v>-4.610763246444808</v>
+        <v>-5.431274946410324</v>
       </c>
       <c r="G5">
-        <v>-8.837611715755564</v>
+        <v>-12.71194647091017</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.736985018127179</v>
       </c>
       <c r="E6">
-        <v>-20.79964094338416</v>
+        <v>-22.97568591591996</v>
       </c>
       <c r="F6">
-        <v>-4.973264820106363</v>
+        <v>-5.831361028857088</v>
       </c>
       <c r="G6">
-        <v>-9.82727282035637</v>
+        <v>-11.47187570171889</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.779505576475152</v>
       </c>
       <c r="E7">
-        <v>-20.62760874430677</v>
+        <v>-22.71840066517417</v>
       </c>
       <c r="F7">
-        <v>-4.754874149926136</v>
+        <v>-4.20772038505392</v>
       </c>
       <c r="G7">
-        <v>-8.085803376514773</v>
+        <v>-11.98760241746318</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.88888290869409</v>
       </c>
       <c r="E8">
-        <v>-21.80970801384702</v>
+        <v>-24.80219609369971</v>
       </c>
       <c r="F8">
-        <v>-4.371108156937976</v>
+        <v>-4.967776487256407</v>
       </c>
       <c r="G8">
-        <v>-8.904776063656298</v>
+        <v>-12.40734648638737</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.029694737931307</v>
       </c>
       <c r="E9">
-        <v>-22.36422418456026</v>
+        <v>-24.21187327900782</v>
       </c>
       <c r="F9">
-        <v>-4.345034022746181</v>
+        <v>-5.28779119047151</v>
       </c>
       <c r="G9">
-        <v>-9.227080845723123</v>
+        <v>-12.7429033822479</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.167725584582444</v>
       </c>
       <c r="E10">
-        <v>-22.30168143004033</v>
+        <v>-26.0224568137026</v>
       </c>
       <c r="F10">
-        <v>-3.986182099366757</v>
+        <v>-4.406967218128313</v>
       </c>
       <c r="G10">
-        <v>-8.539834765589198</v>
+        <v>-12.05266787949201</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.277751928501416</v>
       </c>
       <c r="E11">
-        <v>-22.88026644010434</v>
+        <v>-27.0751730523697</v>
       </c>
       <c r="F11">
-        <v>-4.036411708033792</v>
+        <v>-4.339114921887226</v>
       </c>
       <c r="G11">
-        <v>-9.691047181960901</v>
+        <v>-13.81149451359601</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.331380887580487</v>
       </c>
       <c r="E12">
-        <v>-22.98900868645052</v>
+        <v>-25.05928662006317</v>
       </c>
       <c r="F12">
-        <v>-3.73071766555905</v>
+        <v>-4.404168809775732</v>
       </c>
       <c r="G12">
-        <v>-9.197722927880866</v>
+        <v>-12.90452752602066</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.31184269453208</v>
       </c>
       <c r="E13">
-        <v>-23.60696424953722</v>
+        <v>-26.02702151550233</v>
       </c>
       <c r="F13">
-        <v>-4.11551544295112</v>
+        <v>-4.278076520347317</v>
       </c>
       <c r="G13">
-        <v>-7.903994836589078</v>
+        <v>-12.87856622790169</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.217508154922974</v>
       </c>
       <c r="E14">
-        <v>-25.3137596884502</v>
+        <v>-26.99017812371973</v>
       </c>
       <c r="F14">
-        <v>-3.897038460798501</v>
+        <v>-4.417844110355552</v>
       </c>
       <c r="G14">
-        <v>-7.520759463871967</v>
+        <v>-11.90060128069113</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.047719659550505</v>
       </c>
       <c r="E15">
-        <v>-25.96190658774604</v>
+        <v>-25.92084238544448</v>
       </c>
       <c r="F15">
-        <v>-3.362726175341625</v>
+        <v>-3.936915383896309</v>
       </c>
       <c r="G15">
-        <v>-7.756251810262484</v>
+        <v>-13.2541641720597</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.810546402544469</v>
       </c>
       <c r="E16">
-        <v>-25.43264118809956</v>
+        <v>-27.05480397628319</v>
       </c>
       <c r="F16">
-        <v>-3.659830196931023</v>
+        <v>-3.685433970465933</v>
       </c>
       <c r="G16">
-        <v>-7.186205663309839</v>
+        <v>-13.47567608463788</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.525084510289426</v>
       </c>
       <c r="E17">
-        <v>-26.62780510515194</v>
+        <v>-27.36426177607136</v>
       </c>
       <c r="F17">
-        <v>-3.494252159765913</v>
+        <v>-3.042614074212723</v>
       </c>
       <c r="G17">
-        <v>-7.043236443650874</v>
+        <v>-11.60116574720959</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.208034422765293</v>
       </c>
       <c r="E18">
-        <v>-24.99951982010994</v>
+        <v>-29.19883263758476</v>
       </c>
       <c r="F18">
-        <v>-3.234777782580314</v>
+        <v>-3.570606581214038</v>
       </c>
       <c r="G18">
-        <v>-8.102293203845884</v>
+        <v>-11.23327144252146</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.876390335595125</v>
       </c>
       <c r="E19">
-        <v>-26.85616699241074</v>
+        <v>-27.63012848506168</v>
       </c>
       <c r="F19">
-        <v>-3.343434261732699</v>
+        <v>-2.869241828384778</v>
       </c>
       <c r="G19">
-        <v>-8.288273031151061</v>
+        <v>-10.75318606005297</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.551846219908398</v>
       </c>
       <c r="E20">
-        <v>-27.99736961318772</v>
+        <v>-30.26331611596079</v>
       </c>
       <c r="F20">
-        <v>-2.559914764540018</v>
+        <v>-2.769454894211811</v>
       </c>
       <c r="G20">
-        <v>-6.526999903893542</v>
+        <v>-8.956443747887702</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.250179183087566</v>
       </c>
       <c r="E21">
-        <v>-28.95826651287529</v>
+        <v>-27.49263042876679</v>
       </c>
       <c r="F21">
-        <v>-2.656284853200424</v>
+        <v>-2.363101295604696</v>
       </c>
       <c r="G21">
-        <v>-6.533107860413498</v>
+        <v>-10.30285586089145</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.981602764625852</v>
       </c>
       <c r="E22">
-        <v>-29.08013680536972</v>
+        <v>-27.90095387309041</v>
       </c>
       <c r="F22">
-        <v>-2.314624849386052</v>
+        <v>-2.611776382152914</v>
       </c>
       <c r="G22">
-        <v>-6.314552265001892</v>
+        <v>-10.17221842336627</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.758728203766568</v>
       </c>
       <c r="E23">
-        <v>-29.72247367251371</v>
+        <v>-31.65669813303991</v>
       </c>
       <c r="F23">
-        <v>-2.051755798570709</v>
+        <v>-2.428924864568106</v>
       </c>
       <c r="G23">
-        <v>-6.385129785353615</v>
+        <v>-10.21649034886295</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.588551542833669</v>
       </c>
       <c r="E24">
-        <v>-29.49355478295196</v>
+        <v>-33.34804468287572</v>
       </c>
       <c r="F24">
-        <v>-1.943346377541132</v>
+        <v>-3.074311948110243</v>
       </c>
       <c r="G24">
-        <v>-6.808810092924002</v>
+        <v>-9.476040491367394</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.470598645169186</v>
       </c>
       <c r="E25">
-        <v>-30.33208325800427</v>
+        <v>-32.53828786743115</v>
       </c>
       <c r="F25">
-        <v>-1.968900264339706</v>
+        <v>-2.742839924449894</v>
       </c>
       <c r="G25">
-        <v>-6.883356957377311</v>
+        <v>-7.814259189201594</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.40618155106244</v>
       </c>
       <c r="E26">
-        <v>-29.63013582326031</v>
+        <v>-31.1762949679362</v>
       </c>
       <c r="F26">
-        <v>-1.651852634157178</v>
+        <v>-2.481649601904916</v>
       </c>
       <c r="G26">
-        <v>-7.471630968069183</v>
+        <v>-9.668542093384936</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.393559385379926</v>
       </c>
       <c r="E27">
-        <v>-29.89162802635922</v>
+        <v>-31.9317508515548</v>
       </c>
       <c r="F27">
-        <v>-2.146687090406938</v>
+        <v>-1.784660628520015</v>
       </c>
       <c r="G27">
-        <v>-6.556500175193988</v>
+        <v>-8.72675147728199</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.423451950120735</v>
       </c>
       <c r="E28">
-        <v>-29.61203098417764</v>
+        <v>-33.55693639613855</v>
       </c>
       <c r="F28">
-        <v>-1.771713832661298</v>
+        <v>-2.542999993510167</v>
       </c>
       <c r="G28">
-        <v>-7.321759260960837</v>
+        <v>-9.543340571635238</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.488187724797109</v>
       </c>
       <c r="E29">
-        <v>-29.17208294162145</v>
+        <v>-29.98325037671941</v>
       </c>
       <c r="F29">
-        <v>-1.695090973060506</v>
+        <v>-1.752455176876596</v>
       </c>
       <c r="G29">
-        <v>-6.987900674961955</v>
+        <v>-10.21112395454379</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.579672012006762</v>
       </c>
       <c r="E30">
-        <v>-29.77163705057798</v>
+        <v>-30.55254522235669</v>
       </c>
       <c r="F30">
-        <v>-1.594221575894337</v>
+        <v>-1.957950521640357</v>
       </c>
       <c r="G30">
-        <v>-7.067426599906328</v>
+        <v>-10.11272129893449</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.682505601853055</v>
       </c>
       <c r="E31">
-        <v>-29.02497999195629</v>
+        <v>-31.50681922880804</v>
       </c>
       <c r="F31">
-        <v>-1.97422230806854</v>
+        <v>-2.971755904144131</v>
       </c>
       <c r="G31">
-        <v>-7.433632526369428</v>
+        <v>-8.991538841149517</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.783496552025952</v>
       </c>
       <c r="E32">
-        <v>-29.02762914925078</v>
+        <v>-31.71520601721901</v>
       </c>
       <c r="F32">
-        <v>-1.176993460618857</v>
+        <v>-2.285481493130136</v>
       </c>
       <c r="G32">
-        <v>-7.536951342104542</v>
+        <v>-9.872114159685799</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.872970689660249</v>
       </c>
       <c r="E33">
-        <v>-28.72375495791407</v>
+        <v>-31.79528302309665</v>
       </c>
       <c r="F33">
-        <v>-2.002499377188711</v>
+        <v>-2.548972940370247</v>
       </c>
       <c r="G33">
-        <v>-7.467469612326319</v>
+        <v>-9.552120138405385</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.938128333463821</v>
       </c>
       <c r="E34">
-        <v>-29.29080594468055</v>
+        <v>-31.32963362630993</v>
       </c>
       <c r="F34">
-        <v>-1.953211281688405</v>
+        <v>-2.350656534521173</v>
       </c>
       <c r="G34">
-        <v>-7.352577129385913</v>
+        <v>-11.02986490349756</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.97018258118648</v>
       </c>
       <c r="E35">
-        <v>-28.99042320680376</v>
+        <v>-32.01419851357544</v>
       </c>
       <c r="F35">
-        <v>-2.017218339966806</v>
+        <v>-2.553092951309262</v>
       </c>
       <c r="G35">
-        <v>-6.659825612020181</v>
+        <v>-8.769527036194912</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.965476424100489</v>
       </c>
       <c r="E36">
-        <v>-27.47019636853279</v>
+        <v>-32.64875999084827</v>
       </c>
       <c r="F36">
-        <v>-1.864682121015339</v>
+        <v>-2.588329616074832</v>
       </c>
       <c r="G36">
-        <v>-6.871495272710102</v>
+        <v>-9.727426766891952</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.919961021857713</v>
       </c>
       <c r="E37">
-        <v>-28.69631240542759</v>
+        <v>-30.40115154356926</v>
       </c>
       <c r="F37">
-        <v>-2.289203202031418</v>
+        <v>-2.154479715363858</v>
       </c>
       <c r="G37">
-        <v>-6.873431941850575</v>
+        <v>-11.50498446765715</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.831948599260939</v>
       </c>
       <c r="E38">
-        <v>-29.00366899327619</v>
+        <v>-31.25960983272932</v>
       </c>
       <c r="F38">
-        <v>-1.905913904523806</v>
+        <v>-2.680967701745505</v>
       </c>
       <c r="G38">
-        <v>-6.270690847152088</v>
+        <v>-9.920616962381661</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.704509208154651</v>
       </c>
       <c r="E39">
-        <v>-27.10196350459907</v>
+        <v>-29.84987776024551</v>
       </c>
       <c r="F39">
-        <v>-1.695573211511758</v>
+        <v>-2.851590634104247</v>
       </c>
       <c r="G39">
-        <v>-6.205651869487567</v>
+        <v>-8.724404300494646</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.540992905352087</v>
       </c>
       <c r="E40">
-        <v>-27.74872921932257</v>
+        <v>-31.67023600608584</v>
       </c>
       <c r="F40">
-        <v>-1.591391493423447</v>
+        <v>-2.501186198077777</v>
       </c>
       <c r="G40">
-        <v>-7.799361734274873</v>
+        <v>-8.593962185156283</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.345221373662961</v>
       </c>
       <c r="E41">
-        <v>-27.922554694107</v>
+        <v>-32.5089139207804</v>
       </c>
       <c r="F41">
-        <v>-1.67420189203586</v>
+        <v>-2.33948269743479</v>
       </c>
       <c r="G41">
-        <v>-7.641399053868549</v>
+        <v>-10.25798472665217</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.124935912281352</v>
       </c>
       <c r="E42">
-        <v>-26.25692308392374</v>
+        <v>-28.48700180831906</v>
       </c>
       <c r="F42">
-        <v>-1.668521930770136</v>
+        <v>-2.318006061515515</v>
       </c>
       <c r="G42">
-        <v>-7.505186657655235</v>
+        <v>-9.395057926385743</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.888274045317662</v>
       </c>
       <c r="E43">
-        <v>-26.01806419391516</v>
+        <v>-30.21953256501763</v>
       </c>
       <c r="F43">
-        <v>-1.858524672416111</v>
+        <v>-2.364659662225489</v>
       </c>
       <c r="G43">
-        <v>-6.278202474980695</v>
+        <v>-10.26576119812392</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.642076094737126</v>
       </c>
       <c r="E44">
-        <v>-25.95018236854018</v>
+        <v>-29.98436890979931</v>
       </c>
       <c r="F44">
-        <v>-1.653490186073743</v>
+        <v>-1.513051104757361</v>
       </c>
       <c r="G44">
-        <v>-6.944496112396571</v>
+        <v>-7.992945884683756</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.394344644269515</v>
       </c>
       <c r="E45">
-        <v>-25.38943048911838</v>
+        <v>-28.777435488801</v>
       </c>
       <c r="F45">
-        <v>-2.191608908698378</v>
+        <v>-2.161873246430087</v>
       </c>
       <c r="G45">
-        <v>-7.267717915577774</v>
+        <v>-7.87418999509902</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.152649593466955</v>
       </c>
       <c r="E46">
-        <v>-26.12491806660015</v>
+        <v>-31.27627008860354</v>
       </c>
       <c r="F46">
-        <v>-1.620785867066961</v>
+        <v>-1.649340876575291</v>
       </c>
       <c r="G46">
-        <v>-6.63239443168178</v>
+        <v>-10.08247615488771</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.9213419725226134</v>
       </c>
       <c r="E47">
-        <v>-24.55234206880051</v>
+        <v>-29.87096459946222</v>
       </c>
       <c r="F47">
-        <v>-1.835994080210112</v>
+        <v>-2.054731581985819</v>
       </c>
       <c r="G47">
-        <v>-7.398709581475656</v>
+        <v>-9.382047482416407</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7038615164669757</v>
       </c>
       <c r="E48">
-        <v>-24.49342662196072</v>
+        <v>-29.91008608641449</v>
       </c>
       <c r="F48">
-        <v>-1.544987326395155</v>
+        <v>-2.317062964642871</v>
       </c>
       <c r="G48">
-        <v>-6.35694049008672</v>
+        <v>-7.442110833495502</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5043568273451973</v>
       </c>
       <c r="E49">
-        <v>-23.64666085268846</v>
+        <v>-27.63889108226653</v>
       </c>
       <c r="F49">
-        <v>-1.698100014299841</v>
+        <v>-2.299128287003477</v>
       </c>
       <c r="G49">
-        <v>-7.868297224039117</v>
+        <v>-9.495297934769335</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.3241349528890212</v>
       </c>
       <c r="E50">
-        <v>-23.09111671837547</v>
+        <v>-28.62331793289795</v>
       </c>
       <c r="F50">
-        <v>-1.582190162054744</v>
+        <v>-2.174429658780648</v>
       </c>
       <c r="G50">
-        <v>-5.845934612281438</v>
+        <v>-8.610610918673277</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.163352803674284</v>
       </c>
       <c r="E51">
-        <v>-23.75440683475296</v>
+        <v>-29.01594115783698</v>
       </c>
       <c r="F51">
-        <v>-2.227488558065616</v>
+        <v>-1.673859019705167</v>
       </c>
       <c r="G51">
-        <v>-6.498227952611736</v>
+        <v>-8.014020817586756</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.02456116032711386</v>
       </c>
       <c r="E52">
-        <v>-24.06206230188607</v>
+        <v>-29.36067577014489</v>
       </c>
       <c r="F52">
-        <v>-1.82635802156762</v>
+        <v>-2.394094420369846</v>
       </c>
       <c r="G52">
-        <v>-6.815159719268324</v>
+        <v>-7.924715541119377</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.09170397656617972</v>
       </c>
       <c r="E53">
-        <v>-23.48738083641667</v>
+        <v>-27.96731865967282</v>
       </c>
       <c r="F53">
-        <v>-2.005063397065808</v>
+        <v>-2.417404195886242</v>
       </c>
       <c r="G53">
-        <v>-7.11888240922322</v>
+        <v>-9.864840891136021</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.1856313957393191</v>
       </c>
       <c r="E54">
-        <v>-24.89995226210329</v>
+        <v>-27.59368785472196</v>
       </c>
       <c r="F54">
-        <v>-1.608023572947392</v>
+        <v>-1.22597352531861</v>
       </c>
       <c r="G54">
-        <v>-6.629560604700163</v>
+        <v>-9.237389884532414</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.2551868244842435</v>
       </c>
       <c r="E55">
-        <v>-23.17852079519752</v>
+        <v>-27.11539043003182</v>
       </c>
       <c r="F55">
-        <v>-2.213444254007499</v>
+        <v>-2.011741093058258</v>
       </c>
       <c r="G55">
-        <v>-7.008118176570284</v>
+        <v>-9.873733016454503</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.3008674059386933</v>
       </c>
       <c r="E56">
-        <v>-22.93384734456309</v>
+        <v>-27.27306283803088</v>
       </c>
       <c r="F56">
-        <v>-1.619297975359405</v>
+        <v>-2.619033714510415</v>
       </c>
       <c r="G56">
-        <v>-6.890706368474492</v>
+        <v>-9.49750275809849</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.3243847908722388</v>
       </c>
       <c r="E57">
-        <v>-23.75427550900674</v>
+        <v>-29.94298318584321</v>
       </c>
       <c r="F57">
-        <v>-2.416885532198935</v>
+        <v>-1.8679809804372</v>
       </c>
       <c r="G57">
-        <v>-7.155381173793685</v>
+        <v>-9.253386440578172</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.3269511365555017</v>
       </c>
       <c r="E58">
-        <v>-21.34130530486363</v>
+        <v>-27.99882325334418</v>
       </c>
       <c r="F58">
-        <v>-2.085957511520539</v>
+        <v>-2.707741042098967</v>
       </c>
       <c r="G58">
-        <v>-7.111675351584227</v>
+        <v>-11.22922264532693</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.3115919302498887</v>
       </c>
       <c r="E59">
-        <v>-21.87780720597436</v>
+        <v>-25.6437269470191</v>
       </c>
       <c r="F59">
-        <v>-1.501817878699149</v>
+        <v>-2.576204763586228</v>
       </c>
       <c r="G59">
-        <v>-6.253985834360926</v>
+        <v>-10.35902257651073</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.2824443970806074</v>
       </c>
       <c r="E60">
-        <v>-21.89560863729852</v>
+        <v>-25.61625722368857</v>
       </c>
       <c r="F60">
-        <v>-2.168667344807322</v>
+        <v>-2.682241793154476</v>
       </c>
       <c r="G60">
-        <v>-8.275537362461483</v>
+        <v>-10.12671166438345</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.2436740937328755</v>
       </c>
       <c r="E61">
-        <v>-21.55115931885308</v>
+        <v>-27.30236206486051</v>
       </c>
       <c r="F61">
-        <v>-2.695205217925306</v>
+        <v>-2.872188313240453</v>
       </c>
       <c r="G61">
-        <v>-6.743128869424861</v>
+        <v>-9.69654599810163</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.2001033599273702</v>
       </c>
       <c r="E62">
-        <v>-21.35194721878166</v>
+        <v>-24.12578698812201</v>
       </c>
       <c r="F62">
-        <v>-2.388481766605528</v>
+        <v>-2.900569115098085</v>
       </c>
       <c r="G62">
-        <v>-7.723695905429291</v>
+        <v>-8.953421219810348</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.1567647690757331</v>
       </c>
       <c r="E63">
-        <v>-20.93624689029954</v>
+        <v>-23.11547990853674</v>
       </c>
       <c r="F63">
-        <v>-2.371966089466369</v>
+        <v>-2.638460243122153</v>
       </c>
       <c r="G63">
-        <v>-7.138795340641936</v>
+        <v>-9.866651759546002</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.1190004094834088</v>
       </c>
       <c r="E64">
-        <v>-22.17285087299611</v>
+        <v>-26.31407242590054</v>
       </c>
       <c r="F64">
-        <v>-2.400374606177521</v>
+        <v>-2.530666091840724</v>
       </c>
       <c r="G64">
-        <v>-7.717869345280174</v>
+        <v>-11.37761122803369</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.09140192456305211</v>
       </c>
       <c r="E65">
-        <v>-22.2662461209303</v>
+        <v>-24.90441733747485</v>
       </c>
       <c r="F65">
-        <v>-2.031680742386599</v>
+        <v>-2.956978344247165</v>
       </c>
       <c r="G65">
-        <v>-7.39224408603746</v>
+        <v>-11.66687345507304</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.07710716037204876</v>
       </c>
       <c r="E66">
-        <v>-20.82947000167269</v>
+        <v>-26.64131807159083</v>
       </c>
       <c r="F66">
-        <v>-2.593533673712967</v>
+        <v>-2.89459458453209</v>
       </c>
       <c r="G66">
-        <v>-7.193280299127261</v>
+        <v>-10.7997720568816</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.07859230732124468</v>
       </c>
       <c r="E67">
-        <v>-20.46518596707366</v>
+        <v>-25.13624350734952</v>
       </c>
       <c r="F67">
-        <v>-2.531180004410285</v>
+        <v>-3.032742043388831</v>
       </c>
       <c r="G67">
-        <v>-7.854035393855937</v>
+        <v>-11.06427802437829</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.09691451374922648</v>
       </c>
       <c r="E68">
-        <v>-21.45037812981238</v>
+        <v>-26.02272399366905</v>
       </c>
       <c r="F68">
-        <v>-2.297067093754533</v>
+        <v>-3.351572134579185</v>
       </c>
       <c r="G68">
-        <v>-7.691580303152821</v>
+        <v>-10.63019929326905</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.1315174055671048</v>
       </c>
       <c r="E69">
-        <v>-20.12664630720824</v>
+        <v>-22.83510396882584</v>
       </c>
       <c r="F69">
-        <v>-2.411023444752936</v>
+        <v>-3.238523247070328</v>
       </c>
       <c r="G69">
-        <v>-7.596716620725005</v>
+        <v>-10.89460263385402</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.1826143889405515</v>
       </c>
       <c r="E70">
-        <v>-21.92747550889049</v>
+        <v>-23.90254680496588</v>
       </c>
       <c r="F70">
-        <v>-2.37593485649046</v>
+        <v>-2.827916606227301</v>
       </c>
       <c r="G70">
-        <v>-7.605062506029508</v>
+        <v>-9.996865447242156</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.2504198933498885</v>
       </c>
       <c r="E71">
-        <v>-21.75191562856113</v>
+        <v>-24.196630435498</v>
       </c>
       <c r="F71">
-        <v>-1.998392827749977</v>
+        <v>-4.04072889035928</v>
       </c>
       <c r="G71">
-        <v>-7.619009834386458</v>
+        <v>-11.01194823103903</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.3334783233639809</v>
       </c>
       <c r="E72">
-        <v>-21.31330575007421</v>
+        <v>-25.14544989500712</v>
       </c>
       <c r="F72">
-        <v>-2.889128423564951</v>
+        <v>-2.867939230269329</v>
       </c>
       <c r="G72">
-        <v>-6.932475521543477</v>
+        <v>-10.38367289859614</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.4309277732588619</v>
       </c>
       <c r="E73">
-        <v>-20.4526330371244</v>
+        <v>-24.16666099451524</v>
       </c>
       <c r="F73">
-        <v>-2.831759468631115</v>
+        <v>-2.54364139440592</v>
       </c>
       <c r="G73">
-        <v>-7.828421703018596</v>
+        <v>-10.24856622459294</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.5404902356952843</v>
       </c>
       <c r="E74">
-        <v>-20.29554027379831</v>
+        <v>-23.63136819596456</v>
       </c>
       <c r="F74">
-        <v>-2.617541071685113</v>
+        <v>-3.415738355302087</v>
       </c>
       <c r="G74">
-        <v>-6.44642784655876</v>
+        <v>-9.492341617602765</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.6573342174119737</v>
       </c>
       <c r="E75">
-        <v>-21.11025803251828</v>
+        <v>-24.08229552375234</v>
       </c>
       <c r="F75">
-        <v>-2.795884570381622</v>
+        <v>-3.597710916103826</v>
       </c>
       <c r="G75">
-        <v>-7.454614763997329</v>
+        <v>-10.67283249872378</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.7776808866292167</v>
       </c>
       <c r="E76">
-        <v>-22.31230070158831</v>
+        <v>-25.81790564277613</v>
       </c>
       <c r="F76">
-        <v>-3.301553950651861</v>
+        <v>-3.197422911152844</v>
       </c>
       <c r="G76">
-        <v>-7.184530527266968</v>
+        <v>-10.990154909754</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8969838543967328</v>
       </c>
       <c r="E77">
-        <v>-21.46755010324947</v>
+        <v>-26.15844688815294</v>
       </c>
       <c r="F77">
-        <v>-2.390155743758148</v>
+        <v>-3.633103575902067</v>
       </c>
       <c r="G77">
-        <v>-7.438115005029601</v>
+        <v>-10.33928510400559</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.009648165009801</v>
       </c>
       <c r="E78">
-        <v>-20.35299302353362</v>
+        <v>-26.680385216855</v>
       </c>
       <c r="F78">
-        <v>-2.763759887739891</v>
+        <v>-3.75461974708782</v>
       </c>
       <c r="G78">
-        <v>-7.139315096291602</v>
+        <v>-10.51060252511734</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.111074546998669</v>
       </c>
       <c r="E79">
-        <v>-24.13602133937934</v>
+        <v>-27.7953317453355</v>
       </c>
       <c r="F79">
-        <v>-2.9719681207368</v>
+        <v>-3.438505711542445</v>
       </c>
       <c r="G79">
-        <v>-7.554977262565874</v>
+        <v>-9.720527589988111</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.197050009460407</v>
       </c>
       <c r="E80">
-        <v>-24.05687719914729</v>
+        <v>-27.84828319190719</v>
       </c>
       <c r="F80">
-        <v>-3.514773821018178</v>
+        <v>-3.439520075181284</v>
       </c>
       <c r="G80">
-        <v>-7.306961122400295</v>
+        <v>-8.926499863484995</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.263084422240821</v>
       </c>
       <c r="E81">
-        <v>-24.42761883768125</v>
+        <v>-27.63324860365297</v>
       </c>
       <c r="F81">
-        <v>-3.643632052827908</v>
+        <v>-3.701136414617515</v>
       </c>
       <c r="G81">
-        <v>-6.191277480756051</v>
+        <v>-9.433354317184032</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.304648568345717</v>
       </c>
       <c r="E82">
-        <v>-22.37565405295562</v>
+        <v>-27.70907790091141</v>
       </c>
       <c r="F82">
-        <v>-3.359440777420046</v>
+        <v>-3.831896677231688</v>
       </c>
       <c r="G82">
-        <v>-8.228944744541781</v>
+        <v>-11.20579391454551</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.316878173758955</v>
       </c>
       <c r="E83">
-        <v>-25.90808567416488</v>
+        <v>-30.45418903114709</v>
       </c>
       <c r="F83">
-        <v>-3.005384315552572</v>
+        <v>-3.543294780849327</v>
       </c>
       <c r="G83">
-        <v>-5.860040846824273</v>
+        <v>-11.09860838162053</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.294976112559283</v>
       </c>
       <c r="E84">
-        <v>-24.84668382235107</v>
+        <v>-28.41749426077533</v>
       </c>
       <c r="F84">
-        <v>-2.917019860294713</v>
+        <v>-3.301138227849058</v>
       </c>
       <c r="G84">
-        <v>-7.797345612041457</v>
+        <v>-10.70668944795391</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.233924014364678</v>
       </c>
       <c r="E85">
-        <v>-26.44409397160877</v>
+        <v>-30.5827795790689</v>
       </c>
       <c r="F85">
-        <v>-2.845738048893741</v>
+        <v>-2.715296903021529</v>
       </c>
       <c r="G85">
-        <v>-7.195541401730583</v>
+        <v>-10.67439176567278</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.126940086534058</v>
       </c>
       <c r="E86">
-        <v>-28.69196959885424</v>
+        <v>-30.09693998091898</v>
       </c>
       <c r="F86">
-        <v>-3.286410554688429</v>
+        <v>-3.948909580646889</v>
       </c>
       <c r="G86">
-        <v>-7.604910220934702</v>
+        <v>-9.989820606334586</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9684538884493618</v>
       </c>
       <c r="E87">
-        <v>-29.80870034609376</v>
+        <v>-31.22510286079087</v>
       </c>
       <c r="F87">
-        <v>-2.863660056885811</v>
+        <v>-3.66864114479157</v>
       </c>
       <c r="G87">
-        <v>-6.487379294879545</v>
+        <v>-10.48993478931567</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.7544246284870414</v>
       </c>
       <c r="E88">
-        <v>-29.78641572550201</v>
+        <v>-32.64645046910436</v>
       </c>
       <c r="F88">
-        <v>-3.546104275143316</v>
+        <v>-3.278328903401941</v>
       </c>
       <c r="G88">
-        <v>-6.460871756746601</v>
+        <v>-10.85553488594508</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.4769171997866964</v>
       </c>
       <c r="E89">
-        <v>-31.08516848547985</v>
+        <v>-33.97984152676687</v>
       </c>
       <c r="F89">
-        <v>-3.553327557823636</v>
+        <v>-2.811073893816602</v>
       </c>
       <c r="G89">
-        <v>-7.312145436714793</v>
+        <v>-9.568576860281102</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.1314193661004799</v>
       </c>
       <c r="E90">
-        <v>-32.22834552092417</v>
+        <v>-33.90458055299639</v>
       </c>
       <c r="F90">
-        <v>-3.24955850988911</v>
+        <v>-3.850897188952173</v>
       </c>
       <c r="G90">
-        <v>-6.28703832102501</v>
+        <v>-9.671385852003169</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2804998384315989</v>
       </c>
       <c r="E91">
-        <v>-32.6606472351184</v>
+        <v>-36.58055773479398</v>
       </c>
       <c r="F91">
-        <v>-3.275714996788508</v>
+        <v>-3.397659560424388</v>
       </c>
       <c r="G91">
-        <v>-6.658653678899279</v>
+        <v>-10.30384902455323</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7635754993369714</v>
       </c>
       <c r="E92">
-        <v>-34.85248752499296</v>
+        <v>-38.57728419357404</v>
       </c>
       <c r="F92">
-        <v>-3.425170907734445</v>
+        <v>-3.072367157246084</v>
       </c>
       <c r="G92">
-        <v>-6.810899047159282</v>
+        <v>-10.15818833137084</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.317100586077073</v>
       </c>
       <c r="E93">
-        <v>-35.30906638834232</v>
+        <v>-40.91311863570749</v>
       </c>
       <c r="F93">
-        <v>-3.314718506073951</v>
+        <v>-3.54301921602004</v>
       </c>
       <c r="G93">
-        <v>-5.890587250515128</v>
+        <v>-9.624501906076011</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.931170363873022</v>
       </c>
       <c r="E94">
-        <v>-38.65131115817743</v>
+        <v>-42.96334901488819</v>
       </c>
       <c r="F94">
-        <v>-3.474801875565444</v>
+        <v>-3.007852521221785</v>
       </c>
       <c r="G94">
-        <v>-7.783716096056278</v>
+        <v>-11.01410670673063</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.603310238520429</v>
       </c>
       <c r="E95">
-        <v>-40.09934959229213</v>
+        <v>-43.53492847566233</v>
       </c>
       <c r="F95">
-        <v>-3.385206880811288</v>
+        <v>-3.461712546174337</v>
       </c>
       <c r="G95">
-        <v>-7.611418753464909</v>
+        <v>-10.93092262896536</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.330253901315209</v>
       </c>
       <c r="E96">
-        <v>-42.07797347622653</v>
+        <v>-45.1693339933257</v>
       </c>
       <c r="F96">
-        <v>-3.625966605194139</v>
+        <v>-3.094261099674076</v>
       </c>
       <c r="G96">
-        <v>-7.981203379655961</v>
+        <v>-9.105597066614028</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.088549373424417</v>
       </c>
       <c r="E97">
-        <v>-44.1002065648548</v>
+        <v>-45.67699177924457</v>
       </c>
       <c r="F97">
-        <v>-3.495281568610949</v>
+        <v>-2.809137813334977</v>
       </c>
       <c r="G97">
-        <v>-7.160770741931619</v>
+        <v>-10.46886978804928</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.882489665534312</v>
       </c>
       <c r="E98">
-        <v>-45.69596155686271</v>
+        <v>-48.51628611189179</v>
       </c>
       <c r="F98">
-        <v>-3.919153330201698</v>
+        <v>-3.686668469227018</v>
       </c>
       <c r="G98">
-        <v>-8.276580184306354</v>
+        <v>-11.94376417343215</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.678314121018344</v>
       </c>
       <c r="E99">
-        <v>-47.48565976943411</v>
+        <v>-50.71267751814405</v>
       </c>
       <c r="F99">
-        <v>-4.248417667815924</v>
+        <v>-3.472706632639317</v>
       </c>
       <c r="G99">
-        <v>-7.968146588049075</v>
+        <v>-10.93613342764418</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.490334508577519</v>
       </c>
       <c r="E100">
-        <v>-49.86874204512658</v>
+        <v>-51.50615107317554</v>
       </c>
       <c r="F100">
-        <v>-3.265735273962367</v>
+        <v>-2.873546341062942</v>
       </c>
       <c r="G100">
-        <v>-8.951113769569476</v>
+        <v>-10.79385942254846</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.24942523527862</v>
       </c>
       <c r="E101">
-        <v>-51.99155933417622</v>
+        <v>-52.53543245885294</v>
       </c>
       <c r="F101">
-        <v>-3.764069720285248</v>
+        <v>-2.461324320186166</v>
       </c>
       <c r="G101">
-        <v>-9.236529142692202</v>
+        <v>-10.75282521058919</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.034202094269135</v>
       </c>
       <c r="E102">
-        <v>-54.6506441758067</v>
+        <v>-55.15966616452038</v>
       </c>
       <c r="F102">
-        <v>-3.333760986001195</v>
+        <v>-2.292840974519183</v>
       </c>
       <c r="G102">
-        <v>-8.530048792975114</v>
+        <v>-11.47956609900662</v>
       </c>
     </row>
   </sheetData>
